--- a/docs/ejemplos/proyecto.xlsx
+++ b/docs/ejemplos/proyecto.xlsx
@@ -3104,10 +3104,10 @@
         <v>VAd (−)</v>
       </c>
       <c r="F12" t="str">
-        <v>Dist. adelante/VI (m)</v>
+        <v>Dist. VAd/VI (VA en el BM inicial) (m)</v>
       </c>
       <c r="G12" t="str">
-        <v>Dist. atrás PC (m)</v>
+        <v>Dist. VA en PC (m)</v>
       </c>
       <c r="H12" t="str">
         <v>Subida</v>
@@ -3815,10 +3815,10 @@
         <v>VAd (−)</v>
       </c>
       <c r="F12" t="str">
-        <v>Dist. adelante/VI (m)</v>
+        <v>Dist. VAd/VI (VA en el BM inicial) (m)</v>
       </c>
       <c r="G12" t="str">
-        <v>Dist. atrás PC (m)</v>
+        <v>Dist. VA en PC (m)</v>
       </c>
       <c r="H12" t="str">
         <v>Subida</v>
